--- a/chromadb/docs/dual_qnas.xlsx
+++ b/chromadb/docs/dual_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C806D2F9-0300-483B-928A-B02C06704D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C262B3-DD29-4A13-8D6F-8758F72D15A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -987,9 +987,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="77.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -997,7 +1000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1005,7 +1008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1013,7 +1016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1029,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1045,7 +1048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1053,7 +1056,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1061,7 +1064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1069,7 +1072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1093,7 +1096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1101,7 +1104,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1149,7 +1152,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>

--- a/chromadb/docs/dual_qnas.xlsx
+++ b/chromadb/docs/dual_qnas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C262B3-DD29-4A13-8D6F-8758F72D15A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E959ADD-C5A6-41E3-A15D-5CB07D194144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -1162,5 +1162,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/chromadb/docs/dual_qnas.xlsx
+++ b/chromadb/docs/dual_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E959ADD-C5A6-41E3-A15D-5CB07D194144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF36ECC-DD7B-46DD-BB67-93643298472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>Question</t>
   </si>
@@ -142,10 +142,25 @@
     <t>It depends on your schedule and workload. Dual enrollment can give you a more challenging academic schedule, but you can still participate in extracurriculars if you manage your time effectively.</t>
   </si>
   <si>
-    <t>How do I register for dual enrollment courses?</t>
-  </si>
-  <si>
-    <t>After getting approval from your school and the partnering college, you will typically need to complete a registration process through the college, which may include submitting transcripts, placement tests, or other documentation.</t>
+    <t>scholarships</t>
+  </si>
+  <si>
+    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
+  </si>
+  <si>
+    <t>academic standing</t>
+  </si>
+  <si>
+    <t>What's your Student ID ?</t>
+  </si>
+  <si>
+    <t>graduation</t>
+  </si>
+  <si>
+    <t>To graduate, you must complete a certain number of credits in required subjects (e.g., English, math, science, social studies), pass state exams, and fulfill any additional requirements set by your school.</t>
+  </si>
+  <si>
+    <t>graduation requirements</t>
   </si>
 </sst>
 </file>
@@ -986,13 +1001,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="77.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1008,7 +1023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1016,7 +1031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1024,7 +1039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1032,7 +1047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1040,7 +1055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1048,7 +1063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1056,7 +1071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1064,7 +1079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1080,7 +1095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1103,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1096,7 +1111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1104,7 +1119,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1112,7 +1127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1120,7 +1135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1128,7 +1143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1136,7 +1151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1144,7 +1159,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1152,12 +1167,36 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/dual_qnas.xlsx
+++ b/chromadb/docs/dual_qnas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF36ECC-DD7B-46DD-BB67-93643298472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8996C66-362B-4417-9FAB-720EE7B4BCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>Question</t>
   </si>
@@ -161,6 +161,138 @@
   </si>
   <si>
     <t>graduation requirements</t>
+  </si>
+  <si>
+    <t>AP classes are advanced courses that can help you prepare for college-level work. They are often more challenging, but they can improve your college applications and earn you college credit if you score well on the AP exams.</t>
+  </si>
+  <si>
+    <t>AP tests can show colleges that you are capable of handling rigorous coursework. High scores may also lead to college credit or placement in advanced courses.</t>
+  </si>
+  <si>
+    <t>Choose AP classes that align with your interests and potential college major. You should also consider your workload and how well you feel you can manage advanced courses.</t>
+  </si>
+  <si>
+    <t>Registration for AP classes typically happens during course selection in the spring. Speak with your counselor to make sure you’re enrolled in the courses you want.</t>
+  </si>
+  <si>
+    <t>AP exams are typically registered for through your school, often by the fall of the year you plan to take the exam. Check with your counselor for deadlines and procedures.</t>
+  </si>
+  <si>
+    <t>AP classes help you develop college-level academic skills, improve your GPA (if your school offers weighted grades), and can result in college credit for high scores on AP exams.</t>
+  </si>
+  <si>
+    <t>It’s important to talk to your teacher for extra help or tutoring. If it’s too overwhelming, consider whether switching to a regular course is a better option. Your mental health and well-being are also priorities.</t>
+  </si>
+  <si>
+    <t>Some schools offer weighted GPA for AP courses, meaning you’ll earn extra points for grades in those classes. However, AP exam scores don’t directly affect your GPA, though they can impact your college applications.</t>
+  </si>
+  <si>
+    <t>Begin studying well in advance, review your class materials, take practice exams, and use study guides. Forming or joining a study group can also help reinforce concepts.</t>
+  </si>
+  <si>
+    <t>AP exams are typically held in May. Check the specific dates each year on the College Board website or with your counselor to ensure you're prepared.</t>
+  </si>
+  <si>
+    <t>Talk to your teacher for help, seek tutoring, and consider using online resources or review books. Organize study time to focus on areas where you need the most improvement.</t>
+  </si>
+  <si>
+    <t>Yes, but you should talk to your counselor first to understand the implications, especially regarding your GPA and how dropping the class may affect your overall schedule.</t>
+  </si>
+  <si>
+    <t>AP tests are not mandatory, but if you’re enrolled in an AP class, you are encouraged to take the exam to potentially earn college credit and enhance your application.</t>
+  </si>
+  <si>
+    <t>A low score won’t hurt your high school GPA. Many colleges may not grant credit for lower scores, but it’s still a learning experience. Focus on your performance in the class.</t>
+  </si>
+  <si>
+    <t>Time management is key. Prioritize your tasks, create a study schedule, and learn to say no to overcommitting. It’s important to find balance between academics and personal activities.</t>
+  </si>
+  <si>
+    <t>Yes, taking AP classes demonstrates to colleges that you are ready for the academic challenges of college. A rigorous course load can make your application stand out.</t>
+  </si>
+  <si>
+    <t>AP credit is granted by some colleges based on your score on the AP exam. Typically, a score of 3 or higher is required, though some schools may require a 4 or 5 for credit.</t>
+  </si>
+  <si>
+    <t>It’s usually not required to take the AP exam, but you should check with your school to see if there are any consequences or fees for not taking the exam.</t>
+  </si>
+  <si>
+    <t>The amount of time varies by subject and your comfort level with the material. Generally, it’s recommended to study for at least 1-2 hours a day in the month leading up to the exam.</t>
+  </si>
+  <si>
+    <t>Yes, AP classes that align with your intended major (such as AP Biology for a future in medicine or AP Calculus for engineering) can prepare you for college-level courses in that field and may even provide you with college credit in the subject.</t>
+  </si>
+  <si>
+    <t>Yes you will be able to take any AP exam you wish without taking the class. You can sign up for AP exams by following these steps and working with your guidance counselor.</t>
+  </si>
+  <si>
+    <t>What are AP classes, and are they worth taking?</t>
+  </si>
+  <si>
+    <t>How do AP tests affect my college applications?</t>
+  </si>
+  <si>
+    <t>What AP classes should I take?</t>
+  </si>
+  <si>
+    <t>How do I register for an AP class?</t>
+  </si>
+  <si>
+    <t>How do I register for the AP exams?</t>
+  </si>
+  <si>
+    <t>What are the benefits of taking AP classes?</t>
+  </si>
+  <si>
+    <t>What if I don’t do well in an AP class?</t>
+  </si>
+  <si>
+    <t>How do AP exams impact my GPA?</t>
+  </si>
+  <si>
+    <t>How do I prepare for the AP exams?</t>
+  </si>
+  <si>
+    <t>When are AP exams held?</t>
+  </si>
+  <si>
+    <t>What should I do if I’m struggling in an AP class?</t>
+  </si>
+  <si>
+    <t>Can I drop an AP class if it’s too hard?</t>
+  </si>
+  <si>
+    <t>Are AP tests mandatory?</t>
+  </si>
+  <si>
+    <t>What if I don’t pass the AP exam?</t>
+  </si>
+  <si>
+    <t>How do I balance AP classes with other extracurricular activities?</t>
+  </si>
+  <si>
+    <t>Do AP classes help with college admissions?</t>
+  </si>
+  <si>
+    <t>How do I get AP credit in college?</t>
+  </si>
+  <si>
+    <t>What if I don’t want to take the AP exam after enrolling in the class?</t>
+  </si>
+  <si>
+    <t>How much time should I spend studying for AP exams?</t>
+  </si>
+  <si>
+    <t>Can AP classes help with my college major?</t>
+  </si>
+  <si>
+    <t>Can I take an AP exam without taking the course?</t>
+  </si>
+  <si>
+    <t>counselling</t>
+  </si>
+  <si>
+    <t>Sure, what do you want to know. You can ask things like bullying, FAFSA, SAT, ACT, college, etc.</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.7265625" bestFit="1" customWidth="1"/>
@@ -1169,38 +1301,217 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>46</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B45" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B41" r:id="rId1" display="https://apstudents.collegeboard.org/register-for-ap-exams" xr:uid="{FDAF1BF2-BCD7-45FA-B030-E2F367315BAA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>